--- a/工资表模板.xlsx
+++ b/工资表模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen.changfei\Desktop\工资表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7BC9FF-6756-42F7-A441-D74F469597E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D070FE73-BC33-4F36-9BE2-B9C523D2FFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AE5C5FC7-6F19-4686-87C6-8592E0D5EF2A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="131">
   <si>
     <r>
       <rPr>
@@ -514,14 +514,6 @@
     <t>科室负责人审批：</t>
   </si>
   <si>
-    <t>全勤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>全勤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>查验</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -530,10 +522,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>全勤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>刘雅雯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -551,18 +539,6 @@
   </si>
   <si>
     <t>训犬员</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>全勤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非全勤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非全勤</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -578,7 +554,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -674,26 +650,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -870,11 +832,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -945,9 +907,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -972,23 +931,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1003,93 +950,75 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1483,24 +1412,24 @@
       <c r="P1" s="8"/>
     </row>
     <row r="2" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="82"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="71"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
@@ -1527,54 +1456,54 @@
       <c r="P3" s="13"/>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="77" t="s">
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="78"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="76"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
     </row>
     <row r="5" spans="1:19" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="70" t="s">
+      <c r="A5" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="H5" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="70" t="s">
+      <c r="I5" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="59" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="15" t="s">
@@ -1586,13 +1515,13 @@
       <c r="M5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="70" t="s">
+      <c r="N5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="70" t="s">
+      <c r="O5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="70" t="s">
+      <c r="P5" s="59" t="s">
         <v>16</v>
       </c>
       <c r="S5" s="1" t="s">
@@ -1615,19 +1544,19 @@
       <c r="E6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G6" s="39">
+      <c r="F6" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G6" s="34">
         <v>550</v>
       </c>
-      <c r="H6" s="37">
-        <v>700</v>
-      </c>
-      <c r="I6" s="37">
-        <v>200</v>
-      </c>
-      <c r="J6" s="37">
+      <c r="H6" s="32">
+        <v>700</v>
+      </c>
+      <c r="I6" s="32">
+        <v>200</v>
+      </c>
+      <c r="J6" s="32">
         <v>600</v>
       </c>
       <c r="K6" s="18"/>
@@ -1641,7 +1570,7 @@
         <f t="shared" ref="O6:O38" si="0">N6+F6+G6+H6+I6+J6</f>
         <v>3750</v>
       </c>
-      <c r="P6" s="61"/>
+      <c r="P6" s="51"/>
       <c r="S6" s="1" t="s">
         <v>24</v>
       </c>
@@ -1662,19 +1591,19 @@
       <c r="E7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G7" s="39">
+      <c r="F7" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G7" s="34">
         <v>550</v>
       </c>
-      <c r="H7" s="37">
-        <v>700</v>
-      </c>
-      <c r="I7" s="37">
-        <v>200</v>
-      </c>
-      <c r="J7" s="37">
+      <c r="H7" s="32">
+        <v>700</v>
+      </c>
+      <c r="I7" s="32">
+        <v>200</v>
+      </c>
+      <c r="J7" s="32">
         <v>400</v>
       </c>
       <c r="K7" s="21"/>
@@ -1706,19 +1635,19 @@
       <c r="E8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G8" s="39">
+      <c r="F8" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G8" s="34">
         <v>550</v>
       </c>
-      <c r="H8" s="63">
-        <v>700</v>
-      </c>
-      <c r="I8" s="37">
-        <v>200</v>
-      </c>
-      <c r="J8" s="37">
+      <c r="H8" s="53">
+        <v>700</v>
+      </c>
+      <c r="I8" s="32">
+        <v>200</v>
+      </c>
+      <c r="J8" s="32">
         <v>400</v>
       </c>
       <c r="K8" s="16"/>
@@ -1732,7 +1661,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P8" s="68"/>
+      <c r="P8" s="57"/>
     </row>
     <row r="9" spans="1:19" ht="19.149999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
@@ -1750,23 +1679,23 @@
       <c r="E9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G9" s="39">
-        <v>400</v>
-      </c>
-      <c r="H9" s="37">
-        <v>700</v>
-      </c>
-      <c r="I9" s="37">
-        <v>200</v>
-      </c>
-      <c r="J9" s="37">
-        <v>400</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
+      <c r="F9" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G9" s="34">
+        <v>400</v>
+      </c>
+      <c r="H9" s="32">
+        <v>700</v>
+      </c>
+      <c r="I9" s="32">
+        <v>200</v>
+      </c>
+      <c r="J9" s="32">
+        <v>400</v>
+      </c>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
       <c r="M9" s="21"/>
       <c r="N9" s="16">
         <f t="shared" si="1"/>
@@ -1776,7 +1705,7 @@
         <f t="shared" si="0"/>
         <v>3400</v>
       </c>
-      <c r="P9" s="45"/>
+      <c r="P9" s="38"/>
     </row>
     <row r="10" spans="1:19" ht="19.149999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
@@ -1794,23 +1723,23 @@
       <c r="E10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G10" s="38">
+      <c r="F10" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G10" s="33">
         <v>550</v>
       </c>
-      <c r="H10" s="37">
-        <v>700</v>
-      </c>
-      <c r="I10" s="37">
-        <v>200</v>
-      </c>
-      <c r="J10" s="37">
-        <v>400</v>
-      </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
+      <c r="H10" s="32">
+        <v>700</v>
+      </c>
+      <c r="I10" s="32">
+        <v>200</v>
+      </c>
+      <c r="J10" s="32">
+        <v>400</v>
+      </c>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
       <c r="M10" s="21"/>
       <c r="N10" s="16">
         <f>ROUND((F10+G10)/21.75/8*1.5*K10+(F10+G10)/21.75/8*2*L10+(F10+G10)/21.75/8*3*M10,0)</f>
@@ -1820,7 +1749,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P10" s="64"/>
+      <c r="P10" s="54"/>
     </row>
     <row r="11" spans="1:19" ht="19.149999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
@@ -1829,8 +1758,8 @@
       <c r="B11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="52" t="s">
-        <v>131</v>
+      <c r="C11" s="45" t="s">
+        <v>128</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>26</v>
@@ -1838,23 +1767,23 @@
       <c r="E11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G11" s="38">
+      <c r="F11" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G11" s="33">
         <v>550</v>
       </c>
-      <c r="H11" s="37">
-        <v>700</v>
-      </c>
-      <c r="I11" s="37">
-        <v>200</v>
-      </c>
-      <c r="J11" s="37">
+      <c r="H11" s="32">
+        <v>700</v>
+      </c>
+      <c r="I11" s="32">
+        <v>200</v>
+      </c>
+      <c r="J11" s="32">
         <v>750</v>
       </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
       <c r="M11" s="21"/>
       <c r="N11" s="16">
         <f t="shared" si="1"/>
@@ -1864,7 +1793,7 @@
         <f t="shared" si="0"/>
         <v>3900</v>
       </c>
-      <c r="P11" s="65"/>
+      <c r="P11" s="55"/>
     </row>
     <row r="12" spans="1:19" ht="19.149999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
@@ -1873,8 +1802,8 @@
       <c r="B12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="52" t="s">
-        <v>132</v>
+      <c r="C12" s="45" t="s">
+        <v>129</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>26</v>
@@ -1882,23 +1811,23 @@
       <c r="E12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G12" s="38">
+      <c r="F12" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G12" s="33">
         <v>450</v>
       </c>
-      <c r="H12" s="37">
-        <v>700</v>
-      </c>
-      <c r="I12" s="37">
-        <v>200</v>
-      </c>
-      <c r="J12" s="37">
-        <v>400</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
+      <c r="H12" s="32">
+        <v>700</v>
+      </c>
+      <c r="I12" s="32">
+        <v>200</v>
+      </c>
+      <c r="J12" s="32">
+        <v>400</v>
+      </c>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
       <c r="M12" s="21"/>
       <c r="N12" s="16">
         <f t="shared" si="1"/>
@@ -1908,7 +1837,7 @@
         <f t="shared" si="0"/>
         <v>3450</v>
       </c>
-      <c r="P12" s="45"/>
+      <c r="P12" s="38"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
@@ -1923,22 +1852,22 @@
       <c r="D13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G13" s="39">
+      <c r="E13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G13" s="34">
         <v>550</v>
       </c>
-      <c r="H13" s="37">
-        <v>700</v>
-      </c>
-      <c r="I13" s="37">
-        <v>200</v>
-      </c>
-      <c r="J13" s="37">
+      <c r="H13" s="32">
+        <v>700</v>
+      </c>
+      <c r="I13" s="32">
+        <v>200</v>
+      </c>
+      <c r="J13" s="32">
         <v>400</v>
       </c>
       <c r="K13" s="15"/>
@@ -1952,7 +1881,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P13" s="62"/>
+      <c r="P13" s="52"/>
     </row>
     <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
@@ -1961,28 +1890,28 @@
       <c r="B14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="24" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G14" s="38">
+      <c r="E14" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G14" s="33">
         <v>550</v>
       </c>
-      <c r="H14" s="37">
-        <v>700</v>
-      </c>
-      <c r="I14" s="37">
-        <v>200</v>
-      </c>
-      <c r="J14" s="37">
+      <c r="H14" s="32">
+        <v>700</v>
+      </c>
+      <c r="I14" s="32">
+        <v>200</v>
+      </c>
+      <c r="J14" s="32">
         <v>400</v>
       </c>
       <c r="K14" s="14"/>
@@ -1996,7 +1925,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P14" s="24"/>
+      <c r="P14" s="23"/>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
@@ -2011,22 +1940,22 @@
       <c r="D15" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G15" s="38">
+      <c r="E15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G15" s="33">
         <v>550</v>
       </c>
-      <c r="H15" s="37">
-        <v>700</v>
-      </c>
-      <c r="I15" s="37">
-        <v>200</v>
-      </c>
-      <c r="J15" s="37">
+      <c r="H15" s="32">
+        <v>700</v>
+      </c>
+      <c r="I15" s="32">
+        <v>200</v>
+      </c>
+      <c r="J15" s="32">
         <v>400</v>
       </c>
       <c r="K15" s="15"/>
@@ -2040,7 +1969,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P15" s="24"/>
+      <c r="P15" s="23"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
@@ -2049,28 +1978,28 @@
       <c r="B16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="24" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G16" s="38">
+      <c r="E16" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G16" s="33">
         <v>550</v>
       </c>
-      <c r="H16" s="37">
-        <v>700</v>
-      </c>
-      <c r="I16" s="37">
-        <v>200</v>
-      </c>
-      <c r="J16" s="37">
+      <c r="H16" s="32">
+        <v>700</v>
+      </c>
+      <c r="I16" s="32">
+        <v>200</v>
+      </c>
+      <c r="J16" s="32">
         <v>400</v>
       </c>
       <c r="K16" s="15"/>
@@ -2084,7 +2013,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P16" s="24"/>
+      <c r="P16" s="23"/>
     </row>
     <row r="17" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
@@ -2093,28 +2022,28 @@
       <c r="B17" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G17" s="38">
+      <c r="E17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G17" s="33">
         <v>450</v>
       </c>
-      <c r="H17" s="37">
-        <v>700</v>
-      </c>
-      <c r="I17" s="37">
-        <v>200</v>
-      </c>
-      <c r="J17" s="37">
+      <c r="H17" s="32">
+        <v>700</v>
+      </c>
+      <c r="I17" s="32">
+        <v>200</v>
+      </c>
+      <c r="J17" s="32">
         <v>400</v>
       </c>
       <c r="K17" s="15"/>
@@ -2128,7 +2057,7 @@
         <f t="shared" si="0"/>
         <v>3450</v>
       </c>
-      <c r="P17" s="24"/>
+      <c r="P17" s="23"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
@@ -2137,33 +2066,33 @@
       <c r="B18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G18" s="38">
+      <c r="E18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G18" s="33">
         <v>500</v>
       </c>
-      <c r="H18" s="37">
-        <v>700</v>
-      </c>
-      <c r="I18" s="37">
-        <v>200</v>
-      </c>
-      <c r="J18" s="37">
-        <v>400</v>
-      </c>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
+      <c r="H18" s="32">
+        <v>700</v>
+      </c>
+      <c r="I18" s="32">
+        <v>200</v>
+      </c>
+      <c r="J18" s="32">
+        <v>400</v>
+      </c>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
       <c r="N18" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2172,7 +2101,7 @@
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
-      <c r="P18" s="46"/>
+      <c r="P18" s="39"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
@@ -2181,33 +2110,33 @@
       <c r="B19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="35" t="s">
-        <v>125</v>
+      <c r="C19" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G19" s="38">
+      <c r="E19" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G19" s="33">
         <v>550</v>
       </c>
-      <c r="H19" s="37">
-        <v>700</v>
-      </c>
-      <c r="I19" s="37">
-        <v>200</v>
-      </c>
-      <c r="J19" s="37">
-        <v>400</v>
-      </c>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
+      <c r="H19" s="32">
+        <v>700</v>
+      </c>
+      <c r="I19" s="32">
+        <v>200</v>
+      </c>
+      <c r="J19" s="32">
+        <v>400</v>
+      </c>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
       <c r="N19" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2216,7 +2145,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P19" s="46"/>
+      <c r="P19" s="39"/>
     </row>
     <row r="20" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
@@ -2231,22 +2160,22 @@
       <c r="D20" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G20" s="38">
+      <c r="E20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G20" s="33">
         <v>550</v>
       </c>
-      <c r="H20" s="37">
-        <v>700</v>
-      </c>
-      <c r="I20" s="37">
-        <v>200</v>
-      </c>
-      <c r="J20" s="37">
+      <c r="H20" s="32">
+        <v>700</v>
+      </c>
+      <c r="I20" s="32">
+        <v>200</v>
+      </c>
+      <c r="J20" s="32">
         <v>400</v>
       </c>
       <c r="K20" s="15"/>
@@ -2260,7 +2189,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P20" s="47"/>
+      <c r="P20" s="40"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
@@ -2275,22 +2204,22 @@
       <c r="D21" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G21" s="38">
+      <c r="E21" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G21" s="33">
         <v>550</v>
       </c>
-      <c r="H21" s="37">
-        <v>700</v>
-      </c>
-      <c r="I21" s="37">
-        <v>200</v>
-      </c>
-      <c r="J21" s="37">
+      <c r="H21" s="32">
+        <v>700</v>
+      </c>
+      <c r="I21" s="32">
+        <v>200</v>
+      </c>
+      <c r="J21" s="32">
         <v>400</v>
       </c>
       <c r="K21" s="15"/>
@@ -2304,7 +2233,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P21" s="47"/>
+      <c r="P21" s="40"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
@@ -2319,22 +2248,22 @@
       <c r="D22" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G22" s="38">
+      <c r="E22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G22" s="33">
         <v>550</v>
       </c>
-      <c r="H22" s="37">
-        <v>700</v>
-      </c>
-      <c r="I22" s="37">
-        <v>200</v>
-      </c>
-      <c r="J22" s="37">
+      <c r="H22" s="32">
+        <v>700</v>
+      </c>
+      <c r="I22" s="32">
+        <v>200</v>
+      </c>
+      <c r="J22" s="32">
         <v>400</v>
       </c>
       <c r="K22" s="15"/>
@@ -2348,7 +2277,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P22" s="47"/>
+      <c r="P22" s="40"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
@@ -2363,22 +2292,22 @@
       <c r="D23" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G23" s="38">
+      <c r="E23" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G23" s="33">
         <v>500</v>
       </c>
-      <c r="H23" s="37">
-        <v>700</v>
-      </c>
-      <c r="I23" s="37">
-        <v>200</v>
-      </c>
-      <c r="J23" s="37">
+      <c r="H23" s="32">
+        <v>700</v>
+      </c>
+      <c r="I23" s="32">
+        <v>200</v>
+      </c>
+      <c r="J23" s="32">
         <v>400</v>
       </c>
       <c r="K23" s="15"/>
@@ -2392,7 +2321,7 @@
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
-      <c r="P23" s="47"/>
+      <c r="P23" s="40"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
@@ -2407,27 +2336,27 @@
       <c r="D24" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G24" s="38">
+      <c r="E24" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G24" s="33">
         <v>450</v>
       </c>
-      <c r="H24" s="37">
-        <v>700</v>
-      </c>
-      <c r="I24" s="37">
-        <v>200</v>
-      </c>
-      <c r="J24" s="37">
+      <c r="H24" s="32">
+        <v>700</v>
+      </c>
+      <c r="I24" s="32">
+        <v>200</v>
+      </c>
+      <c r="J24" s="32">
         <v>500</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
       <c r="N24" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2436,7 +2365,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P24" s="62"/>
+      <c r="P24" s="52"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
@@ -2451,27 +2380,27 @@
       <c r="D25" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G25" s="38">
+      <c r="E25" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G25" s="33">
         <v>550</v>
       </c>
-      <c r="H25" s="37">
-        <v>700</v>
-      </c>
-      <c r="I25" s="37">
-        <v>200</v>
-      </c>
-      <c r="J25" s="37">
-        <v>400</v>
-      </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
+      <c r="H25" s="32">
+        <v>700</v>
+      </c>
+      <c r="I25" s="32">
+        <v>200</v>
+      </c>
+      <c r="J25" s="32">
+        <v>400</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
       <c r="N25" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2480,7 +2409,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P25" s="60"/>
+      <c r="P25" s="50"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
@@ -2495,27 +2424,27 @@
       <c r="D26" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G26" s="38">
+      <c r="E26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G26" s="33">
         <v>550</v>
       </c>
-      <c r="H26" s="37">
-        <v>700</v>
-      </c>
-      <c r="I26" s="37">
-        <v>200</v>
-      </c>
-      <c r="J26" s="37">
-        <v>400</v>
-      </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
+      <c r="H26" s="32">
+        <v>700</v>
+      </c>
+      <c r="I26" s="32">
+        <v>200</v>
+      </c>
+      <c r="J26" s="32">
+        <v>400</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
       <c r="N26" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2524,7 +2453,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P26" s="60"/>
+      <c r="P26" s="50"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
@@ -2539,27 +2468,27 @@
       <c r="D27" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G27" s="38">
+      <c r="E27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G27" s="33">
         <v>550</v>
       </c>
-      <c r="H27" s="37">
-        <v>700</v>
-      </c>
-      <c r="I27" s="37">
-        <v>200</v>
-      </c>
-      <c r="J27" s="37">
-        <v>400</v>
-      </c>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
+      <c r="H27" s="32">
+        <v>700</v>
+      </c>
+      <c r="I27" s="32">
+        <v>200</v>
+      </c>
+      <c r="J27" s="32">
+        <v>400</v>
+      </c>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
       <c r="N27" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2568,7 +2497,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P27" s="60"/>
+      <c r="P27" s="50"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
@@ -2583,27 +2512,27 @@
       <c r="D28" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G28" s="38">
+      <c r="E28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G28" s="33">
         <v>550</v>
       </c>
-      <c r="H28" s="37">
-        <v>700</v>
-      </c>
-      <c r="I28" s="37">
-        <v>200</v>
-      </c>
-      <c r="J28" s="37">
-        <v>400</v>
-      </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
+      <c r="H28" s="32">
+        <v>700</v>
+      </c>
+      <c r="I28" s="32">
+        <v>200</v>
+      </c>
+      <c r="J28" s="32">
+        <v>400</v>
+      </c>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
       <c r="N28" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2612,7 +2541,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P28" s="60"/>
+      <c r="P28" s="50"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
@@ -2627,27 +2556,27 @@
       <c r="D29" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G29" s="38">
+      <c r="E29" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G29" s="33">
         <v>500</v>
       </c>
-      <c r="H29" s="37">
-        <v>700</v>
-      </c>
-      <c r="I29" s="37">
-        <v>200</v>
-      </c>
-      <c r="J29" s="37">
-        <v>400</v>
-      </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
+      <c r="H29" s="32">
+        <v>700</v>
+      </c>
+      <c r="I29" s="32">
+        <v>200</v>
+      </c>
+      <c r="J29" s="32">
+        <v>400</v>
+      </c>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
       <c r="N29" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2656,7 +2585,7 @@
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
-      <c r="P29" s="24"/>
+      <c r="P29" s="23"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
@@ -2671,27 +2600,27 @@
       <c r="D30" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G30" s="38">
+      <c r="E30" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G30" s="33">
         <v>550</v>
       </c>
-      <c r="H30" s="37">
-        <v>700</v>
-      </c>
-      <c r="I30" s="37">
-        <v>200</v>
-      </c>
-      <c r="J30" s="37">
-        <v>400</v>
-      </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
+      <c r="H30" s="32">
+        <v>700</v>
+      </c>
+      <c r="I30" s="32">
+        <v>200</v>
+      </c>
+      <c r="J30" s="32">
+        <v>400</v>
+      </c>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
       <c r="N30" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2700,7 +2629,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P30" s="60"/>
+      <c r="P30" s="50"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
@@ -2709,33 +2638,33 @@
       <c r="B31" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="26" t="s">
         <v>57</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G31" s="38">
+      <c r="E31" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G31" s="33">
         <v>550</v>
       </c>
-      <c r="H31" s="37">
-        <v>700</v>
-      </c>
-      <c r="I31" s="37">
-        <v>200</v>
-      </c>
-      <c r="J31" s="37">
-        <v>400</v>
-      </c>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
+      <c r="H31" s="32">
+        <v>700</v>
+      </c>
+      <c r="I31" s="32">
+        <v>200</v>
+      </c>
+      <c r="J31" s="32">
+        <v>400</v>
+      </c>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
       <c r="N31" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2744,7 +2673,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P31" s="60"/>
+      <c r="P31" s="50"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
@@ -2759,27 +2688,27 @@
       <c r="D32" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E32" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G32" s="38">
+      <c r="E32" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G32" s="33">
         <v>450</v>
       </c>
-      <c r="H32" s="37">
-        <v>700</v>
-      </c>
-      <c r="I32" s="37">
-        <v>200</v>
-      </c>
-      <c r="J32" s="37">
-        <v>400</v>
-      </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
+      <c r="H32" s="32">
+        <v>700</v>
+      </c>
+      <c r="I32" s="32">
+        <v>200</v>
+      </c>
+      <c r="J32" s="32">
+        <v>400</v>
+      </c>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
       <c r="N32" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2788,7 +2717,7 @@
         <f t="shared" si="0"/>
         <v>3450</v>
       </c>
-      <c r="P32" s="60"/>
+      <c r="P32" s="50"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
@@ -2803,27 +2732,27 @@
       <c r="D33" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G33" s="38">
+      <c r="E33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G33" s="33">
         <v>550</v>
       </c>
-      <c r="H33" s="37">
-        <v>700</v>
-      </c>
-      <c r="I33" s="37">
-        <v>200</v>
-      </c>
-      <c r="J33" s="37">
-        <v>400</v>
-      </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
+      <c r="H33" s="32">
+        <v>700</v>
+      </c>
+      <c r="I33" s="32">
+        <v>200</v>
+      </c>
+      <c r="J33" s="32">
+        <v>400</v>
+      </c>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
       <c r="N33" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2832,7 +2761,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P33" s="60"/>
+      <c r="P33" s="50"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
@@ -2847,27 +2776,27 @@
       <c r="D34" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G34" s="38">
+      <c r="E34" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G34" s="33">
         <v>450</v>
       </c>
-      <c r="H34" s="37">
-        <v>700</v>
-      </c>
-      <c r="I34" s="37">
-        <v>200</v>
-      </c>
-      <c r="J34" s="37">
-        <v>400</v>
-      </c>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
+      <c r="H34" s="32">
+        <v>700</v>
+      </c>
+      <c r="I34" s="32">
+        <v>200</v>
+      </c>
+      <c r="J34" s="32">
+        <v>400</v>
+      </c>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
       <c r="N34" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2876,7 +2805,7 @@
         <f t="shared" si="0"/>
         <v>3450</v>
       </c>
-      <c r="P34" s="60"/>
+      <c r="P34" s="50"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
@@ -2891,27 +2820,27 @@
       <c r="D35" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G35" s="38">
+      <c r="E35" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G35" s="33">
         <v>450</v>
       </c>
-      <c r="H35" s="37">
-        <v>700</v>
-      </c>
-      <c r="I35" s="37">
-        <v>200</v>
-      </c>
-      <c r="J35" s="37">
-        <v>400</v>
-      </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
+      <c r="H35" s="32">
+        <v>700</v>
+      </c>
+      <c r="I35" s="32">
+        <v>200</v>
+      </c>
+      <c r="J35" s="32">
+        <v>400</v>
+      </c>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
       <c r="N35" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2920,7 +2849,7 @@
         <f t="shared" si="0"/>
         <v>3450</v>
       </c>
-      <c r="P35" s="60"/>
+      <c r="P35" s="50"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
@@ -2935,27 +2864,27 @@
       <c r="D36" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G36" s="38">
+      <c r="E36" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G36" s="33">
         <v>550</v>
       </c>
-      <c r="H36" s="37">
-        <v>700</v>
-      </c>
-      <c r="I36" s="37">
-        <v>200</v>
-      </c>
-      <c r="J36" s="37">
-        <v>400</v>
-      </c>
-      <c r="K36" s="30"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
+      <c r="H36" s="32">
+        <v>700</v>
+      </c>
+      <c r="I36" s="32">
+        <v>200</v>
+      </c>
+      <c r="J36" s="32">
+        <v>400</v>
+      </c>
+      <c r="K36" s="29"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
       <c r="N36" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2964,7 +2893,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P36" s="24"/>
+      <c r="P36" s="23"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
@@ -2979,27 +2908,27 @@
       <c r="D37" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G37" s="38">
+      <c r="E37" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G37" s="33">
         <v>550</v>
       </c>
-      <c r="H37" s="37">
-        <v>700</v>
-      </c>
-      <c r="I37" s="37">
-        <v>200</v>
-      </c>
-      <c r="J37" s="37">
-        <v>400</v>
-      </c>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
+      <c r="H37" s="32">
+        <v>700</v>
+      </c>
+      <c r="I37" s="32">
+        <v>200</v>
+      </c>
+      <c r="J37" s="32">
+        <v>400</v>
+      </c>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
       <c r="N37" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3008,7 +2937,7 @@
         <f t="shared" si="0"/>
         <v>3550</v>
       </c>
-      <c r="P37" s="60"/>
+      <c r="P37" s="50"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="16">
@@ -3023,27 +2952,27 @@
       <c r="D38" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G38" s="38">
+      <c r="E38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G38" s="33">
         <v>500</v>
       </c>
-      <c r="H38" s="37">
-        <v>700</v>
-      </c>
-      <c r="I38" s="37">
-        <v>200</v>
-      </c>
-      <c r="J38" s="37">
-        <v>400</v>
-      </c>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
+      <c r="H38" s="32">
+        <v>700</v>
+      </c>
+      <c r="I38" s="32">
+        <v>200</v>
+      </c>
+      <c r="J38" s="32">
+        <v>400</v>
+      </c>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
       <c r="N38" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3052,7 +2981,7 @@
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
-      <c r="P38" s="60"/>
+      <c r="P38" s="50"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="16">
@@ -3067,24 +2996,24 @@
       <c r="D39" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F39" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G39" s="38">
+      <c r="E39" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G39" s="33">
         <v>450</v>
       </c>
-      <c r="H39" s="37">
-        <v>700</v>
-      </c>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37">
+      <c r="H39" s="32">
+        <v>700</v>
+      </c>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32">
         <v>500</v>
       </c>
       <c r="K39" s="14"/>
-      <c r="L39" s="42"/>
+      <c r="L39" s="36"/>
       <c r="M39" s="15"/>
       <c r="N39" s="16">
         <f t="shared" si="1"/>
@@ -3094,7 +3023,7 @@
         <f t="shared" ref="O39:O69" si="2">N39+F39+G39+H39+I39+J39</f>
         <v>3350</v>
       </c>
-      <c r="P39" s="60"/>
+      <c r="P39" s="50"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="16">
@@ -3109,26 +3038,26 @@
       <c r="D40" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G40" s="38">
+      <c r="E40" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G40" s="33">
         <v>450</v>
       </c>
-      <c r="H40" s="37">
-        <v>700</v>
-      </c>
-      <c r="I40" s="37">
-        <v>200</v>
-      </c>
-      <c r="J40" s="37">
+      <c r="H40" s="32">
+        <v>700</v>
+      </c>
+      <c r="I40" s="32">
+        <v>200</v>
+      </c>
+      <c r="J40" s="32">
         <v>400</v>
       </c>
       <c r="K40" s="14"/>
-      <c r="L40" s="42"/>
+      <c r="L40" s="36"/>
       <c r="M40" s="15"/>
       <c r="N40" s="16">
         <f t="shared" si="1"/>
@@ -3138,7 +3067,7 @@
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="P40" s="60"/>
+      <c r="P40" s="50"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="16">
@@ -3153,26 +3082,26 @@
       <c r="D41" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G41" s="38">
+      <c r="E41" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G41" s="33">
         <v>450</v>
       </c>
-      <c r="H41" s="37">
-        <v>700</v>
-      </c>
-      <c r="I41" s="37">
-        <v>200</v>
-      </c>
-      <c r="J41" s="37">
+      <c r="H41" s="32">
+        <v>700</v>
+      </c>
+      <c r="I41" s="32">
+        <v>200</v>
+      </c>
+      <c r="J41" s="32">
         <v>400</v>
       </c>
       <c r="K41" s="14"/>
-      <c r="L41" s="42"/>
+      <c r="L41" s="36"/>
       <c r="M41" s="15"/>
       <c r="N41" s="16">
         <f t="shared" si="1"/>
@@ -3182,7 +3111,7 @@
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="P41" s="60"/>
+      <c r="P41" s="50"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="16">
@@ -3191,32 +3120,32 @@
       <c r="B42" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="26" t="s">
         <v>57</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G42" s="38">
+      <c r="E42" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G42" s="33">
         <v>550</v>
       </c>
-      <c r="H42" s="37">
-        <v>700</v>
-      </c>
-      <c r="I42" s="37">
-        <v>200</v>
-      </c>
-      <c r="J42" s="37">
+      <c r="H42" s="32">
+        <v>700</v>
+      </c>
+      <c r="I42" s="32">
+        <v>200</v>
+      </c>
+      <c r="J42" s="32">
         <v>400</v>
       </c>
       <c r="K42" s="14"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="36"/>
       <c r="M42" s="15"/>
       <c r="N42" s="16">
         <f t="shared" si="1"/>
@@ -3226,7 +3155,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P42" s="60"/>
+      <c r="P42" s="50"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="16">
@@ -3241,26 +3170,26 @@
       <c r="D43" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G43" s="38">
+      <c r="E43" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G43" s="33">
         <v>550</v>
       </c>
-      <c r="H43" s="37">
-        <v>700</v>
-      </c>
-      <c r="I43" s="37">
-        <v>200</v>
-      </c>
-      <c r="J43" s="37">
+      <c r="H43" s="32">
+        <v>700</v>
+      </c>
+      <c r="I43" s="32">
+        <v>200</v>
+      </c>
+      <c r="J43" s="32">
         <v>400</v>
       </c>
       <c r="K43" s="14"/>
-      <c r="L43" s="42"/>
+      <c r="L43" s="36"/>
       <c r="M43" s="15"/>
       <c r="N43" s="16">
         <f t="shared" si="1"/>
@@ -3270,7 +3199,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P43" s="60"/>
+      <c r="P43" s="50"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="16">
@@ -3285,26 +3214,26 @@
       <c r="D44" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G44" s="38">
+      <c r="E44" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G44" s="33">
         <v>450</v>
       </c>
-      <c r="H44" s="37">
-        <v>700</v>
-      </c>
-      <c r="I44" s="37">
-        <v>200</v>
-      </c>
-      <c r="J44" s="37">
+      <c r="H44" s="32">
+        <v>700</v>
+      </c>
+      <c r="I44" s="32">
+        <v>200</v>
+      </c>
+      <c r="J44" s="32">
         <v>400</v>
       </c>
       <c r="K44" s="14"/>
-      <c r="L44" s="42"/>
+      <c r="L44" s="36"/>
       <c r="M44" s="15"/>
       <c r="N44" s="16">
         <f t="shared" si="1"/>
@@ -3314,7 +3243,7 @@
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="P44" s="60"/>
+      <c r="P44" s="50"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45" s="16">
@@ -3329,26 +3258,26 @@
       <c r="D45" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E45" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G45" s="38">
+      <c r="E45" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G45" s="33">
         <v>500</v>
       </c>
-      <c r="H45" s="37">
-        <v>700</v>
-      </c>
-      <c r="I45" s="37">
-        <v>200</v>
-      </c>
-      <c r="J45" s="37">
+      <c r="H45" s="32">
+        <v>700</v>
+      </c>
+      <c r="I45" s="32">
+        <v>200</v>
+      </c>
+      <c r="J45" s="32">
         <v>400</v>
       </c>
       <c r="K45" s="14"/>
-      <c r="L45" s="42"/>
+      <c r="L45" s="36"/>
       <c r="M45" s="15"/>
       <c r="N45" s="16">
         <f t="shared" si="1"/>
@@ -3358,7 +3287,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P45" s="60"/>
+      <c r="P45" s="50"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46" s="16">
@@ -3373,26 +3302,26 @@
       <c r="D46" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G46" s="38">
+      <c r="E46" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G46" s="33">
         <v>550</v>
       </c>
-      <c r="H46" s="37">
-        <v>700</v>
-      </c>
-      <c r="I46" s="37">
-        <v>200</v>
-      </c>
-      <c r="J46" s="37">
+      <c r="H46" s="32">
+        <v>700</v>
+      </c>
+      <c r="I46" s="32">
+        <v>200</v>
+      </c>
+      <c r="J46" s="32">
         <v>400</v>
       </c>
       <c r="K46" s="14"/>
-      <c r="L46" s="42"/>
+      <c r="L46" s="36"/>
       <c r="M46" s="15"/>
       <c r="N46" s="16">
         <f t="shared" si="1"/>
@@ -3402,7 +3331,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P46" s="60"/>
+      <c r="P46" s="50"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47" s="16">
@@ -3417,26 +3346,26 @@
       <c r="D47" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G47" s="38">
+      <c r="E47" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G47" s="33">
         <v>550</v>
       </c>
-      <c r="H47" s="37">
-        <v>700</v>
-      </c>
-      <c r="I47" s="37">
-        <v>200</v>
-      </c>
-      <c r="J47" s="37">
+      <c r="H47" s="32">
+        <v>700</v>
+      </c>
+      <c r="I47" s="32">
+        <v>200</v>
+      </c>
+      <c r="J47" s="32">
         <v>400</v>
       </c>
       <c r="K47" s="14"/>
-      <c r="L47" s="42"/>
+      <c r="L47" s="36"/>
       <c r="M47" s="15"/>
       <c r="N47" s="16">
         <f t="shared" si="1"/>
@@ -3446,7 +3375,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P47" s="60"/>
+      <c r="P47" s="50"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48" s="16">
@@ -3461,26 +3390,26 @@
       <c r="D48" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G48" s="38">
+      <c r="E48" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G48" s="33">
         <v>500</v>
       </c>
-      <c r="H48" s="37">
-        <v>700</v>
-      </c>
-      <c r="I48" s="37">
-        <v>200</v>
-      </c>
-      <c r="J48" s="37">
+      <c r="H48" s="32">
+        <v>700</v>
+      </c>
+      <c r="I48" s="32">
+        <v>200</v>
+      </c>
+      <c r="J48" s="32">
         <v>400</v>
       </c>
       <c r="K48" s="14"/>
-      <c r="L48" s="42"/>
+      <c r="L48" s="36"/>
       <c r="M48" s="15"/>
       <c r="N48" s="16">
         <f t="shared" si="1"/>
@@ -3490,7 +3419,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P48" s="47"/>
+      <c r="P48" s="40"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49" s="16">
@@ -3505,26 +3434,26 @@
       <c r="D49" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E49" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G49" s="38">
+      <c r="E49" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G49" s="33">
         <v>550</v>
       </c>
-      <c r="H49" s="37">
-        <v>700</v>
-      </c>
-      <c r="I49" s="37">
-        <v>200</v>
-      </c>
-      <c r="J49" s="37">
+      <c r="H49" s="32">
+        <v>700</v>
+      </c>
+      <c r="I49" s="32">
+        <v>200</v>
+      </c>
+      <c r="J49" s="32">
         <v>400</v>
       </c>
       <c r="K49" s="14"/>
-      <c r="L49" s="42"/>
+      <c r="L49" s="36"/>
       <c r="M49" s="15"/>
       <c r="N49" s="16">
         <f t="shared" si="1"/>
@@ -3534,7 +3463,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P49" s="47"/>
+      <c r="P49" s="40"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50" s="16">
@@ -3549,26 +3478,26 @@
       <c r="D50" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E50" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G50" s="38">
+      <c r="E50" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G50" s="33">
         <v>500</v>
       </c>
-      <c r="H50" s="37">
-        <v>700</v>
-      </c>
-      <c r="I50" s="37">
-        <v>200</v>
-      </c>
-      <c r="J50" s="37">
+      <c r="H50" s="32">
+        <v>700</v>
+      </c>
+      <c r="I50" s="32">
+        <v>200</v>
+      </c>
+      <c r="J50" s="32">
         <v>400</v>
       </c>
       <c r="K50" s="14"/>
-      <c r="L50" s="42"/>
+      <c r="L50" s="36"/>
       <c r="M50" s="15"/>
       <c r="N50" s="16">
         <f t="shared" si="1"/>
@@ -3578,7 +3507,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P50" s="47"/>
+      <c r="P50" s="40"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51" s="16">
@@ -3587,32 +3516,32 @@
       <c r="B51" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="24" t="s">
         <v>78</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G51" s="38">
+      <c r="E51" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G51" s="33">
         <v>550</v>
       </c>
-      <c r="H51" s="37">
-        <v>700</v>
-      </c>
-      <c r="I51" s="37">
-        <v>200</v>
-      </c>
-      <c r="J51" s="37">
+      <c r="H51" s="32">
+        <v>700</v>
+      </c>
+      <c r="I51" s="32">
+        <v>200</v>
+      </c>
+      <c r="J51" s="32">
         <v>400</v>
       </c>
       <c r="K51" s="14"/>
-      <c r="L51" s="42"/>
+      <c r="L51" s="36"/>
       <c r="M51" s="15"/>
       <c r="N51" s="16">
         <f t="shared" si="1"/>
@@ -3622,7 +3551,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P51" s="47"/>
+      <c r="P51" s="40"/>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52" s="16">
@@ -3637,26 +3566,26 @@
       <c r="D52" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E52" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G52" s="38">
-        <v>400</v>
-      </c>
-      <c r="H52" s="37">
-        <v>700</v>
-      </c>
-      <c r="I52" s="37">
-        <v>200</v>
-      </c>
-      <c r="J52" s="37">
+      <c r="E52" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G52" s="33">
+        <v>400</v>
+      </c>
+      <c r="H52" s="32">
+        <v>700</v>
+      </c>
+      <c r="I52" s="32">
+        <v>200</v>
+      </c>
+      <c r="J52" s="32">
         <v>400</v>
       </c>
       <c r="K52" s="14"/>
-      <c r="L52" s="42"/>
+      <c r="L52" s="36"/>
       <c r="M52" s="15"/>
       <c r="N52" s="16">
         <f t="shared" si="1"/>
@@ -3666,7 +3595,7 @@
         <f t="shared" si="2"/>
         <v>3400</v>
       </c>
-      <c r="P52" s="47"/>
+      <c r="P52" s="40"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53" s="16">
@@ -3675,32 +3604,32 @@
       <c r="B53" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="51" t="s">
-        <v>130</v>
+      <c r="C53" s="44" t="s">
+        <v>127</v>
       </c>
       <c r="D53" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G53" s="38">
-        <v>400</v>
-      </c>
-      <c r="H53" s="37">
-        <v>700</v>
-      </c>
-      <c r="I53" s="37">
-        <v>200</v>
-      </c>
-      <c r="J53" s="37">
+      <c r="E53" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G53" s="33">
+        <v>400</v>
+      </c>
+      <c r="H53" s="32">
+        <v>700</v>
+      </c>
+      <c r="I53" s="32">
+        <v>200</v>
+      </c>
+      <c r="J53" s="32">
         <v>400</v>
       </c>
       <c r="K53" s="14"/>
-      <c r="L53" s="42"/>
+      <c r="L53" s="36"/>
       <c r="M53" s="15"/>
       <c r="N53" s="16">
         <f t="shared" si="1"/>
@@ -3710,7 +3639,7 @@
         <f t="shared" si="2"/>
         <v>3400</v>
       </c>
-      <c r="P53" s="47"/>
+      <c r="P53" s="40"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54" s="16">
@@ -3725,26 +3654,26 @@
       <c r="D54" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E54" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G54" s="38">
+      <c r="E54" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G54" s="33">
         <v>450</v>
       </c>
-      <c r="H54" s="37">
-        <v>700</v>
-      </c>
-      <c r="I54" s="37">
-        <v>200</v>
-      </c>
-      <c r="J54" s="37">
+      <c r="H54" s="32">
+        <v>700</v>
+      </c>
+      <c r="I54" s="32">
+        <v>200</v>
+      </c>
+      <c r="J54" s="32">
         <v>500</v>
       </c>
       <c r="K54" s="15"/>
-      <c r="L54" s="39"/>
+      <c r="L54" s="34"/>
       <c r="M54" s="15"/>
       <c r="N54" s="16">
         <f t="shared" si="1"/>
@@ -3754,7 +3683,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P54" s="53"/>
+      <c r="P54" s="46"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55" s="16">
@@ -3769,26 +3698,26 @@
       <c r="D55" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G55" s="38">
+      <c r="E55" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G55" s="33">
         <v>450</v>
       </c>
-      <c r="H55" s="37">
-        <v>700</v>
-      </c>
-      <c r="I55" s="37">
-        <v>200</v>
-      </c>
-      <c r="J55" s="37">
+      <c r="H55" s="32">
+        <v>700</v>
+      </c>
+      <c r="I55" s="32">
+        <v>200</v>
+      </c>
+      <c r="J55" s="32">
         <v>400</v>
       </c>
       <c r="K55" s="15"/>
-      <c r="L55" s="39"/>
+      <c r="L55" s="34"/>
       <c r="M55" s="15"/>
       <c r="N55" s="16">
         <f t="shared" si="1"/>
@@ -3798,7 +3727,7 @@
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="P55" s="57"/>
+      <c r="P55" s="47"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
@@ -3813,26 +3742,26 @@
       <c r="D56" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E56" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G56" s="38">
+      <c r="E56" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G56" s="33">
         <v>550</v>
       </c>
-      <c r="H56" s="37">
-        <v>700</v>
-      </c>
-      <c r="I56" s="37">
-        <v>200</v>
-      </c>
-      <c r="J56" s="37">
+      <c r="H56" s="32">
+        <v>700</v>
+      </c>
+      <c r="I56" s="32">
+        <v>200</v>
+      </c>
+      <c r="J56" s="32">
         <v>400</v>
       </c>
       <c r="K56" s="15"/>
-      <c r="L56" s="39"/>
+      <c r="L56" s="34"/>
       <c r="M56" s="15"/>
       <c r="N56" s="16">
         <f t="shared" si="1"/>
@@ -3842,7 +3771,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P56" s="61"/>
+      <c r="P56" s="51"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57" s="16">
@@ -3851,32 +3780,32 @@
       <c r="B57" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G57" s="38">
+      <c r="E57" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G57" s="33">
         <v>550</v>
       </c>
-      <c r="H57" s="37">
-        <v>700</v>
-      </c>
-      <c r="I57" s="37">
-        <v>200</v>
-      </c>
-      <c r="J57" s="37">
+      <c r="H57" s="32">
+        <v>700</v>
+      </c>
+      <c r="I57" s="32">
+        <v>200</v>
+      </c>
+      <c r="J57" s="32">
         <v>400</v>
       </c>
       <c r="K57" s="15"/>
-      <c r="L57" s="39"/>
+      <c r="L57" s="34"/>
       <c r="M57" s="15"/>
       <c r="N57" s="16">
         <f t="shared" si="1"/>
@@ -3886,7 +3815,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P57" s="57"/>
+      <c r="P57" s="47"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58" s="16">
@@ -3901,26 +3830,26 @@
       <c r="D58" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E58" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G58" s="38">
+      <c r="E58" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G58" s="33">
         <v>550</v>
       </c>
-      <c r="H58" s="37">
-        <v>700</v>
-      </c>
-      <c r="I58" s="37">
-        <v>200</v>
-      </c>
-      <c r="J58" s="37">
+      <c r="H58" s="32">
+        <v>700</v>
+      </c>
+      <c r="I58" s="32">
+        <v>200</v>
+      </c>
+      <c r="J58" s="32">
         <v>400</v>
       </c>
       <c r="K58" s="15"/>
-      <c r="L58" s="39"/>
+      <c r="L58" s="34"/>
       <c r="M58" s="15"/>
       <c r="N58" s="16">
         <f t="shared" si="1"/>
@@ -3930,7 +3859,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P58" s="57"/>
+      <c r="P58" s="47"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
@@ -3945,26 +3874,26 @@
       <c r="D59" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E59" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G59" s="38">
+      <c r="E59" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G59" s="33">
         <v>550</v>
       </c>
-      <c r="H59" s="37">
-        <v>700</v>
-      </c>
-      <c r="I59" s="37">
-        <v>200</v>
-      </c>
-      <c r="J59" s="37">
+      <c r="H59" s="32">
+        <v>700</v>
+      </c>
+      <c r="I59" s="32">
+        <v>200</v>
+      </c>
+      <c r="J59" s="32">
         <v>400</v>
       </c>
       <c r="K59" s="15"/>
-      <c r="L59" s="39"/>
+      <c r="L59" s="34"/>
       <c r="M59" s="15"/>
       <c r="N59" s="16">
         <f t="shared" si="1"/>
@@ -3974,7 +3903,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P59" s="57"/>
+      <c r="P59" s="47"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60" s="16">
@@ -3989,26 +3918,26 @@
       <c r="D60" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E60" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G60" s="38">
+      <c r="E60" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G60" s="33">
         <v>550</v>
       </c>
-      <c r="H60" s="37">
-        <v>700</v>
-      </c>
-      <c r="I60" s="37">
-        <v>200</v>
-      </c>
-      <c r="J60" s="37">
+      <c r="H60" s="32">
+        <v>700</v>
+      </c>
+      <c r="I60" s="32">
+        <v>200</v>
+      </c>
+      <c r="J60" s="32">
         <v>400</v>
       </c>
       <c r="K60" s="15"/>
-      <c r="L60" s="39"/>
+      <c r="L60" s="34"/>
       <c r="M60" s="15"/>
       <c r="N60" s="16">
         <f t="shared" si="1"/>
@@ -4018,7 +3947,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P60" s="58"/>
+      <c r="P60" s="48"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61" s="16">
@@ -4033,26 +3962,26 @@
       <c r="D61" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E61" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="F61" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G61" s="38">
+      <c r="E61" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G61" s="33">
         <v>550</v>
       </c>
-      <c r="H61" s="37">
-        <v>700</v>
-      </c>
-      <c r="I61" s="37">
-        <v>200</v>
-      </c>
-      <c r="J61" s="37">
+      <c r="H61" s="32">
+        <v>700</v>
+      </c>
+      <c r="I61" s="32">
+        <v>200</v>
+      </c>
+      <c r="J61" s="32">
         <v>400</v>
       </c>
       <c r="K61" s="15"/>
-      <c r="L61" s="39"/>
+      <c r="L61" s="34"/>
       <c r="M61" s="15"/>
       <c r="N61" s="16">
         <f t="shared" si="1"/>
@@ -4062,7 +3991,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P61" s="59"/>
+      <c r="P61" s="49"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62" s="16">
@@ -4077,26 +4006,26 @@
       <c r="D62" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E62" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G62" s="38">
+      <c r="E62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G62" s="33">
         <v>500</v>
       </c>
-      <c r="H62" s="37">
-        <v>700</v>
-      </c>
-      <c r="I62" s="37">
-        <v>200</v>
-      </c>
-      <c r="J62" s="37">
+      <c r="H62" s="32">
+        <v>700</v>
+      </c>
+      <c r="I62" s="32">
+        <v>200</v>
+      </c>
+      <c r="J62" s="32">
         <v>400</v>
       </c>
       <c r="K62" s="15"/>
-      <c r="L62" s="39"/>
+      <c r="L62" s="34"/>
       <c r="M62" s="15"/>
       <c r="N62" s="16">
         <f t="shared" si="1"/>
@@ -4106,7 +4035,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P62" s="57"/>
+      <c r="P62" s="47"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63" s="16">
@@ -4121,26 +4050,26 @@
       <c r="D63" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G63" s="38">
+      <c r="E63" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G63" s="33">
         <v>500</v>
       </c>
-      <c r="H63" s="37">
-        <v>700</v>
-      </c>
-      <c r="I63" s="37">
-        <v>200</v>
-      </c>
-      <c r="J63" s="37">
+      <c r="H63" s="32">
+        <v>700</v>
+      </c>
+      <c r="I63" s="32">
+        <v>200</v>
+      </c>
+      <c r="J63" s="32">
         <v>400</v>
       </c>
       <c r="K63" s="15"/>
-      <c r="L63" s="39"/>
+      <c r="L63" s="34"/>
       <c r="M63" s="15"/>
       <c r="N63" s="16">
         <f t="shared" si="1"/>
@@ -4150,7 +4079,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P63" s="57"/>
+      <c r="P63" s="47"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64" s="16">
@@ -4165,26 +4094,26 @@
       <c r="D64" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E64" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G64" s="38">
+      <c r="E64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G64" s="33">
         <v>500</v>
       </c>
-      <c r="H64" s="37">
-        <v>700</v>
-      </c>
-      <c r="I64" s="37">
-        <v>200</v>
-      </c>
-      <c r="J64" s="37">
+      <c r="H64" s="32">
+        <v>700</v>
+      </c>
+      <c r="I64" s="32">
+        <v>200</v>
+      </c>
+      <c r="J64" s="32">
         <v>400</v>
       </c>
       <c r="K64" s="15"/>
-      <c r="L64" s="39"/>
+      <c r="L64" s="34"/>
       <c r="M64" s="15"/>
       <c r="N64" s="16">
         <f t="shared" si="1"/>
@@ -4194,7 +4123,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P64" s="57"/>
+      <c r="P64" s="47"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65" s="16">
@@ -4209,26 +4138,26 @@
       <c r="D65" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E65" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G65" s="38">
+      <c r="E65" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G65" s="33">
         <v>450</v>
       </c>
-      <c r="H65" s="37">
-        <v>700</v>
-      </c>
-      <c r="I65" s="37">
-        <v>200</v>
-      </c>
-      <c r="J65" s="37">
+      <c r="H65" s="32">
+        <v>700</v>
+      </c>
+      <c r="I65" s="32">
+        <v>200</v>
+      </c>
+      <c r="J65" s="32">
         <v>400</v>
       </c>
       <c r="K65" s="15"/>
-      <c r="L65" s="39"/>
+      <c r="L65" s="34"/>
       <c r="M65" s="15"/>
       <c r="N65" s="16">
         <f t="shared" si="1"/>
@@ -4238,7 +4167,7 @@
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="P65" s="57"/>
+      <c r="P65" s="47"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66" s="16">
@@ -4253,26 +4182,26 @@
       <c r="D66" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G66" s="38">
+      <c r="E66" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G66" s="33">
         <v>550</v>
       </c>
-      <c r="H66" s="37">
-        <v>700</v>
-      </c>
-      <c r="I66" s="37">
-        <v>200</v>
-      </c>
-      <c r="J66" s="37">
+      <c r="H66" s="32">
+        <v>700</v>
+      </c>
+      <c r="I66" s="32">
+        <v>200</v>
+      </c>
+      <c r="J66" s="32">
         <v>400</v>
       </c>
       <c r="K66" s="15"/>
-      <c r="L66" s="39"/>
+      <c r="L66" s="34"/>
       <c r="M66" s="15"/>
       <c r="N66" s="16">
         <f t="shared" si="1"/>
@@ -4282,7 +4211,7 @@
         <f t="shared" si="2"/>
         <v>3550</v>
       </c>
-      <c r="P66" s="53"/>
+      <c r="P66" s="46"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67" s="16">
@@ -4297,26 +4226,26 @@
       <c r="D67" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E67" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G67" s="38">
+      <c r="E67" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G67" s="33">
         <v>500</v>
       </c>
-      <c r="H67" s="37">
-        <v>700</v>
-      </c>
-      <c r="I67" s="37">
-        <v>200</v>
-      </c>
-      <c r="J67" s="37">
+      <c r="H67" s="32">
+        <v>700</v>
+      </c>
+      <c r="I67" s="32">
+        <v>200</v>
+      </c>
+      <c r="J67" s="32">
         <v>400</v>
       </c>
       <c r="K67" s="15"/>
-      <c r="L67" s="39"/>
+      <c r="L67" s="34"/>
       <c r="M67" s="15"/>
       <c r="N67" s="16">
         <f t="shared" si="1"/>
@@ -4326,7 +4255,7 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P67" s="53"/>
+      <c r="P67" s="46"/>
     </row>
     <row r="68" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="16">
@@ -4341,22 +4270,22 @@
       <c r="D68" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E68" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G68" s="38">
+      <c r="E68" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G68" s="33">
         <v>500</v>
       </c>
-      <c r="H68" s="37">
-        <v>700</v>
-      </c>
-      <c r="I68" s="37">
-        <v>200</v>
-      </c>
-      <c r="J68" s="37">
+      <c r="H68" s="32">
+        <v>700</v>
+      </c>
+      <c r="I68" s="32">
+        <v>200</v>
+      </c>
+      <c r="J68" s="32">
         <v>400</v>
       </c>
       <c r="K68" s="15"/>
@@ -4370,14 +4299,14 @@
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="P68" s="47"/>
+      <c r="P68" s="40"/>
     </row>
     <row r="69" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="16">
         <v>64</v>
       </c>
-      <c r="B69" s="40" t="s">
-        <v>128</v>
+      <c r="B69" s="35" t="s">
+        <v>125</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>22</v>
@@ -4385,22 +4314,22 @@
       <c r="D69" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E69" s="54" t="s">
-        <v>133</v>
-      </c>
-      <c r="F69" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G69" s="38">
-        <v>400</v>
-      </c>
-      <c r="H69" s="37">
-        <v>700</v>
-      </c>
-      <c r="I69" s="37">
-        <v>200</v>
-      </c>
-      <c r="J69" s="37">
+      <c r="E69" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G69" s="33">
+        <v>400</v>
+      </c>
+      <c r="H69" s="32">
+        <v>700</v>
+      </c>
+      <c r="I69" s="32">
+        <v>200</v>
+      </c>
+      <c r="J69" s="32">
         <v>400</v>
       </c>
       <c r="K69" s="15"/>
@@ -4414,7 +4343,7 @@
         <f t="shared" si="2"/>
         <v>3400</v>
       </c>
-      <c r="P69" s="47"/>
+      <c r="P69" s="40"/>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="16">
@@ -4429,22 +4358,22 @@
       <c r="D70" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G70" s="38">
+      <c r="E70" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G70" s="33">
         <v>450</v>
       </c>
-      <c r="H70" s="37">
-        <v>700</v>
-      </c>
-      <c r="I70" s="37">
-        <v>200</v>
-      </c>
-      <c r="J70" s="37">
+      <c r="H70" s="32">
+        <v>700</v>
+      </c>
+      <c r="I70" s="32">
+        <v>200</v>
+      </c>
+      <c r="J70" s="32">
         <v>400</v>
       </c>
       <c r="K70" s="15"/>
@@ -4458,7 +4387,7 @@
         <f>N70+F70+G70+H70+I70+J70</f>
         <v>3450</v>
       </c>
-      <c r="P70" s="47"/>
+      <c r="P70" s="40"/>
     </row>
     <row r="71" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="16">
@@ -4467,28 +4396,28 @@
       <c r="B71" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E71" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G71" s="38">
+      <c r="E71" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G71" s="33">
         <v>450</v>
       </c>
-      <c r="H71" s="37">
-        <v>700</v>
-      </c>
-      <c r="I71" s="37">
-        <v>200</v>
-      </c>
-      <c r="J71" s="37">
+      <c r="H71" s="32">
+        <v>700</v>
+      </c>
+      <c r="I71" s="32">
+        <v>200</v>
+      </c>
+      <c r="J71" s="32">
         <v>400</v>
       </c>
       <c r="K71" s="14"/>
@@ -4498,11 +4427,11 @@
         <f>ROUND((F71+G71)/21.75/8*1.5*K71+(F71+G71)/21.75/8*2*L71+(F71+G71)/21.75/8*3*M71,0)</f>
         <v>0</v>
       </c>
-      <c r="O71" s="38">
+      <c r="O71" s="33">
         <f>N71+F71+G71+H71+I71+J71</f>
         <v>3450</v>
       </c>
-      <c r="P71" s="47"/>
+      <c r="P71" s="40"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A72" s="16">
@@ -4511,28 +4440,28 @@
       <c r="B72" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="26" t="s">
         <v>57</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G72" s="38">
-        <v>400</v>
-      </c>
-      <c r="H72" s="37">
-        <v>700</v>
-      </c>
-      <c r="I72" s="37">
-        <v>200</v>
-      </c>
-      <c r="J72" s="37">
+      <c r="E72" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G72" s="33">
+        <v>400</v>
+      </c>
+      <c r="H72" s="32">
+        <v>700</v>
+      </c>
+      <c r="I72" s="32">
+        <v>200</v>
+      </c>
+      <c r="J72" s="32">
         <v>400</v>
       </c>
       <c r="K72" s="15"/>
@@ -4546,7 +4475,7 @@
         <f>N72+F72+G72+H72+I72+J72</f>
         <v>3400</v>
       </c>
-      <c r="P72" s="47"/>
+      <c r="P72" s="40"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A73" s="16">
@@ -4555,28 +4484,28 @@
       <c r="B73" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="C73" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E73" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="37">
-        <v>1700</v>
-      </c>
-      <c r="G73" s="38">
+      <c r="E73" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="32">
+        <v>1700</v>
+      </c>
+      <c r="G73" s="33">
         <v>500</v>
       </c>
-      <c r="H73" s="37">
-        <v>700</v>
-      </c>
-      <c r="I73" s="37">
-        <v>200</v>
-      </c>
-      <c r="J73" s="37">
+      <c r="H73" s="32">
+        <v>700</v>
+      </c>
+      <c r="I73" s="32">
+        <v>200</v>
+      </c>
+      <c r="J73" s="32">
         <v>400</v>
       </c>
       <c r="K73" s="16"/>
@@ -4590,7 +4519,7 @@
         <f>N73+F73+G73+H73+I73+J73</f>
         <v>3500</v>
       </c>
-      <c r="P73" s="47"/>
+      <c r="P73" s="40"/>
     </row>
     <row r="74" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="16">
@@ -4618,7 +4547,7 @@
       <c r="M74" s="15"/>
       <c r="N74" s="16"/>
       <c r="O74" s="16"/>
-      <c r="P74" s="47"/>
+      <c r="P74" s="40"/>
     </row>
     <row r="75" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="16">
@@ -4646,7 +4575,7 @@
       <c r="M75" s="15"/>
       <c r="N75" s="16"/>
       <c r="O75" s="16"/>
-      <c r="P75" s="47"/>
+      <c r="P75" s="40"/>
     </row>
     <row r="76" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="16">
@@ -4674,7 +4603,7 @@
       <c r="M76" s="14"/>
       <c r="N76" s="16"/>
       <c r="O76" s="16"/>
-      <c r="P76" s="47"/>
+      <c r="P76" s="40"/>
     </row>
     <row r="77" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="16">
@@ -4702,7 +4631,7 @@
       <c r="M77" s="14"/>
       <c r="N77" s="16"/>
       <c r="O77" s="16"/>
-      <c r="P77" s="47"/>
+      <c r="P77" s="40"/>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="16">
@@ -4717,8 +4646,8 @@
       <c r="D78" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E78" s="36" t="s">
-        <v>123</v>
+      <c r="E78" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="F78" s="14"/>
       <c r="G78" s="14"/>
@@ -4730,7 +4659,7 @@
       <c r="M78" s="14"/>
       <c r="N78" s="16"/>
       <c r="O78" s="16"/>
-      <c r="P78" s="47"/>
+      <c r="P78" s="40"/>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="16">
@@ -4745,8 +4674,8 @@
       <c r="D79" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="36" t="s">
-        <v>124</v>
+      <c r="E79" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="F79" s="14"/>
       <c r="G79" s="14"/>
@@ -4758,7 +4687,7 @@
       <c r="M79" s="14"/>
       <c r="N79" s="16"/>
       <c r="O79" s="16"/>
-      <c r="P79" s="47"/>
+      <c r="P79" s="40"/>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="16">
@@ -4773,8 +4702,8 @@
       <c r="D80" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E80" s="36" t="s">
-        <v>127</v>
+      <c r="E80" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="F80" s="14"/>
       <c r="G80" s="14"/>
@@ -4786,7 +4715,7 @@
       <c r="M80" s="14"/>
       <c r="N80" s="16"/>
       <c r="O80" s="16"/>
-      <c r="P80" s="47"/>
+      <c r="P80" s="40"/>
     </row>
     <row r="81" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="16">
@@ -4814,7 +4743,7 @@
       <c r="M81" s="14"/>
       <c r="N81" s="16"/>
       <c r="O81" s="16"/>
-      <c r="P81" s="47"/>
+      <c r="P81" s="40"/>
     </row>
     <row r="82" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="16">
@@ -4842,7 +4771,7 @@
       <c r="M82" s="14"/>
       <c r="N82" s="16"/>
       <c r="O82" s="16"/>
-      <c r="P82" s="47"/>
+      <c r="P82" s="40"/>
     </row>
     <row r="83" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="16">
@@ -4870,7 +4799,7 @@
       <c r="M83" s="14"/>
       <c r="N83" s="16"/>
       <c r="O83" s="16"/>
-      <c r="P83" s="47"/>
+      <c r="P83" s="40"/>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16">
@@ -4898,7 +4827,7 @@
       <c r="M84" s="14"/>
       <c r="N84" s="16"/>
       <c r="O84" s="16"/>
-      <c r="P84" s="48"/>
+      <c r="P84" s="41"/>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="16">
@@ -4926,7 +4855,7 @@
       <c r="M85" s="14"/>
       <c r="N85" s="16"/>
       <c r="O85" s="16"/>
-      <c r="P85" s="49"/>
+      <c r="P85" s="42"/>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="16">
@@ -4954,7 +4883,7 @@
       <c r="M86" s="14"/>
       <c r="N86" s="16"/>
       <c r="O86" s="16"/>
-      <c r="P86" s="47"/>
+      <c r="P86" s="40"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87" s="16">
@@ -4969,8 +4898,8 @@
       <c r="D87" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E87" s="66" t="s">
-        <v>135</v>
+      <c r="E87" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="F87" s="14"/>
       <c r="G87" s="14"/>
@@ -4982,7 +4911,7 @@
       <c r="M87" s="14"/>
       <c r="N87" s="16"/>
       <c r="O87" s="16"/>
-      <c r="P87" s="67"/>
+      <c r="P87" s="56"/>
     </row>
     <row r="88" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16">
@@ -5010,7 +4939,7 @@
       <c r="M88" s="14"/>
       <c r="N88" s="16"/>
       <c r="O88" s="16"/>
-      <c r="P88" s="50"/>
+      <c r="P88" s="43"/>
     </row>
     <row r="89" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16">
@@ -5038,14 +4967,14 @@
       <c r="M89" s="14"/>
       <c r="N89" s="16"/>
       <c r="O89" s="16"/>
-      <c r="P89" s="47"/>
+      <c r="P89" s="40"/>
     </row>
     <row r="90" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16">
         <v>85</v>
       </c>
-      <c r="B90" s="36" t="s">
-        <v>126</v>
+      <c r="B90" s="31" t="s">
+        <v>124</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>113</v>
@@ -5066,51 +4995,51 @@
       <c r="M90" s="14"/>
       <c r="N90" s="16"/>
       <c r="O90" s="16"/>
-      <c r="P90" s="47"/>
+      <c r="P90" s="40"/>
     </row>
     <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="14"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="29">
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="28">
         <f t="shared" ref="F91:O91" si="3">SUM(F6:F89)</f>
         <v>115600</v>
       </c>
-      <c r="G91" s="29">
+      <c r="G91" s="28">
         <f t="shared" si="3"/>
         <v>34500</v>
       </c>
-      <c r="H91" s="29">
+      <c r="H91" s="28">
         <f t="shared" si="3"/>
         <v>47600</v>
       </c>
-      <c r="I91" s="29">
+      <c r="I91" s="28">
         <f t="shared" si="3"/>
         <v>13400</v>
       </c>
-      <c r="J91" s="29">
+      <c r="J91" s="28">
         <f t="shared" si="3"/>
         <v>28050</v>
       </c>
-      <c r="K91" s="29">
+      <c r="K91" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L91" s="29">
+      <c r="L91" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M91" s="29">
+      <c r="M91" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N91" s="29">
+      <c r="N91" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O91" s="29">
+      <c r="O91" s="28">
         <f t="shared" si="3"/>
         <v>239150</v>
       </c>
@@ -5135,8 +5064,8 @@
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
-      <c r="O92" s="44" t="s">
-        <v>129</v>
+      <c r="O92" s="37" t="s">
+        <v>126</v>
       </c>
       <c r="P92" s="8"/>
     </row>
